--- a/Test Cases/E-commerce Test Cases.xlsx
+++ b/Test Cases/E-commerce Test Cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="102">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -37,13 +37,16 @@
     <t>Type</t>
   </si>
   <si>
+    <t>Screenshot</t>
+  </si>
+  <si>
     <t>TC-001</t>
   </si>
   <si>
     <t>User registers with valid details</t>
   </si>
   <si>
-    <t>User is on the registration page</t>
+    <t>User is on the signup page</t>
   </si>
   <si>
     <r>
@@ -52,7 +55,7 @@
         <color theme="1"/>
         <sz val="12.0"/>
       </rPr>
-      <t xml:space="preserve">1. Open the Registration page.
+      <t xml:space="preserve">1. Open the signup page.
 2. Enter valid details
 3. Click </t>
     </r>
@@ -63,14 +66,14 @@
         <color theme="1"/>
         <sz val="12.0"/>
       </rPr>
-      <t>Register</t>
+      <t>Signup</t>
     </r>
   </si>
   <si>
     <t>Account is created successfully.</t>
   </si>
   <si>
-    <t>As Expected</t>
+    <t>Accounted created successfully</t>
   </si>
   <si>
     <t>Pass</t>
@@ -82,7 +85,7 @@
     <t>TC-002</t>
   </si>
   <si>
-    <t>Register using an email address that already exists</t>
+    <t>Register with existing email</t>
   </si>
   <si>
     <t>The email address is already registered</t>
@@ -94,7 +97,7 @@
         <color theme="1"/>
         <sz val="12.0"/>
       </rPr>
-      <t xml:space="preserve">1. Open the Registration page.
+      <t xml:space="preserve">1. Open the signup page.
 2. Enter an existing email address and other valid details.
 3. Click </t>
     </r>
@@ -105,7 +108,7 @@
         <color theme="1"/>
         <sz val="12.0"/>
       </rPr>
-      <t>Register</t>
+      <t>Signup</t>
     </r>
     <r>
       <rPr>
@@ -117,7 +120,10 @@
     </r>
   </si>
   <si>
-    <t>Registration is rejected, and an appropriate message is displayed indicating the email is already in use.</t>
+    <t>Registration is rejected with an error message</t>
+  </si>
+  <si>
+    <t>"Email Address already exists!" displayed</t>
   </si>
   <si>
     <t>Negative</t>
@@ -146,7 +152,7 @@
         <color theme="1"/>
         <sz val="12.0"/>
       </rPr>
-      <t>Register</t>
+      <t>Signup</t>
     </r>
     <r>
       <rPr>
@@ -158,136 +164,28 @@
     </r>
   </si>
   <si>
-    <t>Registration succeeds if the username meets the system's character limit.</t>
+    <t>System displays validation message</t>
+  </si>
+  <si>
+    <t>Registration accepted without validation</t>
+  </si>
+  <si>
+    <t>Fail</t>
   </si>
   <si>
     <t>Edge Case</t>
   </si>
   <si>
+    <t>https://youtu.be/7XAjstgHvr8</t>
+  </si>
+  <si>
     <t>TC-004</t>
   </si>
   <si>
-    <t>Login with an invalid password</t>
+    <t>Login with valid details</t>
   </si>
   <si>
     <t>User account exists</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t xml:space="preserve">1. Open the login page.
-2. Enter a valid username.
-3. Enter an invalid password.
-4. Click the </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>Login</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t xml:space="preserve"> button.</t>
-    </r>
-  </si>
-  <si>
-    <t>An error message such as "Invalid username or password" is displayed, and the user remains on the login page.</t>
-  </si>
-  <si>
-    <t>TC-005</t>
-  </si>
-  <si>
-    <t>Login without entering credentials</t>
-  </si>
-  <si>
-    <t>User is on the Login Page</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t xml:space="preserve">1. Leave the username and password fields empty.
-2. Click </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>Login</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Validation messages are displayed, and login is prevented.</t>
-  </si>
-  <si>
-    <t>TC-006</t>
-  </si>
-  <si>
-    <t>Login using a password with the minimum allowed length</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t xml:space="preserve">1. Enter a valid username.
-2. Enter a password that is exactly the minimum required length.
-3. Click </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>Login</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Login is successful if the password satisfies the minimum length requirement.</t>
-  </si>
-  <si>
-    <t>TC-007</t>
-  </si>
-  <si>
-    <t>User logs in with valid credentials</t>
   </si>
   <si>
     <r>
@@ -323,13 +221,13 @@
     <t>User is redirected to the dashboard/home page.</t>
   </si>
   <si>
-    <t>TC-008</t>
+    <t>Login Successful</t>
   </si>
   <si>
-    <t>Search returns matching products</t>
+    <t>TC-005</t>
   </si>
   <si>
-    <t>User is on the homepage</t>
+    <t>Login with incorrect Password</t>
   </si>
   <si>
     <r>
@@ -338,8 +236,9 @@
         <color theme="1"/>
         <sz val="12.0"/>
       </rPr>
-      <t xml:space="preserve">1. Type a Valid Product name
-2. Click </t>
+      <t xml:space="preserve">1. Enter correct email
+2. Enter incorrect password
+3. Click </t>
     </r>
     <r>
       <rPr>
@@ -348,36 +247,7 @@
         <color theme="1"/>
         <sz val="12.0"/>
       </rPr>
-      <t>Search</t>
-    </r>
-  </si>
-  <si>
-    <t>Relevant products are displayed.</t>
-  </si>
-  <si>
-    <t>TC-009</t>
-  </si>
-  <si>
-    <t>Search for a product that does not exist</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t xml:space="preserve">1. Enter a non-existing product name.
-2. Click </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <b/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>Search</t>
+      <t>Login</t>
     </r>
     <r>
       <rPr>
@@ -389,10 +259,126 @@
     </r>
   </si>
   <si>
+    <t>Login rejected with error message</t>
+  </si>
+  <si>
+    <t>Error message displayed "Your email or password is incorrecr"</t>
+  </si>
+  <si>
+    <t>TC-006</t>
+  </si>
+  <si>
+    <t>Login with spaces before email</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Times New Roman"/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve">1. Add spaces before/after email 
+2. Click </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Times New Roman"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>Login</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Times New Roman"/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>System trims spaces and logs user in</t>
+  </si>
+  <si>
+    <t>Login failed due to spaces being included</t>
+  </si>
+  <si>
+    <t>https://prnt.sc/dSuXBOmAKxfV</t>
+  </si>
+  <si>
+    <t>TC-007</t>
+  </si>
+  <si>
+    <t>Search existing product</t>
+  </si>
+  <si>
+    <t>User is on product page</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Times New Roman"/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve">1. Search "Blue Top"
+2. Click the </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Times New Roman"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>Search Icon</t>
+    </r>
+  </si>
+  <si>
+    <t>Matching products displayed</t>
+  </si>
+  <si>
+    <t>Product displayed</t>
+  </si>
+  <si>
+    <t>TC-008</t>
+  </si>
+  <si>
+    <t>Search invalid product name</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Times New Roman"/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve">1. Search "xyz123notfound"
+2. Click the </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Times New Roman"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>Search Icon</t>
+    </r>
+  </si>
+  <si>
     <t>A "No products found" message is displayed.</t>
   </si>
   <si>
-    <t>TC-010</t>
+    <t>No products shown but no message displayed</t>
+  </si>
+  <si>
+    <t>https://prnt.sc/YQxvqO8BKMU7</t>
+  </si>
+  <si>
+    <t>TC-009</t>
   </si>
   <si>
     <t>Search using only special characters</t>
@@ -404,8 +390,8 @@
         <color theme="1"/>
         <sz val="12.0"/>
       </rPr>
-      <t xml:space="preserve">1. Enter special characters (e.g., @#$%^&amp;*) in the search box.
-2. Click </t>
+      <t xml:space="preserve">1. Search "@#$%^&amp;*"
+2. Click the </t>
     </r>
     <r>
       <rPr>
@@ -414,28 +400,23 @@
         <color theme="1"/>
         <sz val="12.0"/>
       </rPr>
-      <t>Search</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <color theme="1"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t>.</t>
+      <t>Search Icon</t>
     </r>
   </si>
   <si>
-    <t>The application handles the input gracefully without crashing and displays an appropriate response.</t>
+    <t>Application handles input safely</t>
   </si>
   <si>
-    <t>TC-011</t>
+    <t>No crash, no results displayed</t>
   </si>
   <si>
-    <t>Add selected product to cart</t>
+    <t>TC-010</t>
   </si>
   <si>
-    <t>User is logged in</t>
+    <t>Add product to cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product is available </t>
   </si>
   <si>
     <r>
@@ -444,8 +425,7 @@
         <color theme="1"/>
         <sz val="12.0"/>
       </rPr>
-      <t xml:space="preserve">1. Select a Product
-2. Click </t>
+      <t xml:space="preserve">1. Click </t>
     </r>
     <r>
       <rPr>
@@ -454,37 +434,49 @@
         <color theme="1"/>
         <sz val="12.0"/>
       </rPr>
-      <t>Add to Cart</t>
+      <t xml:space="preserve">Add to Cart </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Times New Roman"/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>on a product image</t>
     </r>
   </si>
   <si>
     <t>Product appears in the shopping cart.</t>
   </si>
   <si>
+    <t>Product added successfully</t>
+  </si>
+  <si>
+    <t>TC-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add maximum quantity of product </t>
+  </si>
+  <si>
+    <t>Product is already in cart</t>
+  </si>
+  <si>
+    <t>1. Increase the quantity to the maximum allowed.</t>
+  </si>
+  <si>
+    <t>Quantity limit is enforced or updated correctly</t>
+  </si>
+  <si>
+    <t>Quantity updated without error</t>
+  </si>
+  <si>
     <t>TC-012</t>
   </si>
   <si>
-    <t>Add the maximum allowable quantity of a product to the cart</t>
+    <t>Checkout with an empty cart</t>
   </si>
   <si>
-    <t>Product is available in sufficient quantity</t>
-  </si>
-  <si>
-    <t>1. Select a product.
-2. Increase the quantity to the maximum allowed.
-3. Add the product to the cart.</t>
-  </si>
-  <si>
-    <t>The system allows the maximum permitted quantity and updates the cart correctly.</t>
-  </si>
-  <si>
-    <t>TC-013</t>
-  </si>
-  <si>
-    <t>Attempt checkout with an empty shopping cart</t>
-  </si>
-  <si>
-    <t>Cart contains no products</t>
+    <t>User has empty cart</t>
   </si>
   <si>
     <r>
@@ -518,29 +510,16 @@
     <t>Checkout is blocked, and the user is informed that the cart is empty.</t>
   </si>
   <si>
-    <t>TC-014</t>
+    <t>Checkout blocked with a message "Cart is empty!"</t>
   </si>
   <si>
-    <t>Logout while the application is open in multiple browser tabs</t>
+    <t>TC-013</t>
   </si>
   <si>
-    <t>User is logged in and has the application open in two browser tabs</t>
+    <t>Complete checkout successfully</t>
   </si>
   <si>
-    <t>1. Log out from one browser tab.
-2. Refresh the second browser tab.</t>
-  </si>
-  <si>
-    <t>The session ends in all tabs, and the user is redirected to the Login page.</t>
-  </si>
-  <si>
-    <t>TC-015</t>
-  </si>
-  <si>
-    <t>Complete checkout and logout</t>
-  </si>
-  <si>
-    <t>User has items in the cart</t>
+    <t>User logged in with cart items</t>
   </si>
   <si>
     <r>
@@ -549,10 +528,7 @@
         <color theme="1"/>
         <sz val="12.0"/>
       </rPr>
-      <t xml:space="preserve">1. Proceed to Checkout
-2. Enter required details 
-3. Place the Order
-4. Click </t>
+      <t xml:space="preserve">1. Click </t>
     </r>
     <r>
       <rPr>
@@ -561,18 +537,116 @@
         <color theme="1"/>
         <sz val="12.0"/>
       </rPr>
-      <t>Logout</t>
+      <t>Proceed to checkout</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Times New Roman"/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve">.
+2. Enter checkout details and confirm order by clicking </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Times New Roman"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>Place Order</t>
     </r>
   </si>
   <si>
-    <t>Order is placed successfully and the user is logged out.</t>
+    <t>Order placed successfully</t>
+  </si>
+  <si>
+    <t>Order confirmation displayed</t>
+  </si>
+  <si>
+    <t>TC-014</t>
+  </si>
+  <si>
+    <t>Attempt checkout with missing required information</t>
+  </si>
+  <si>
+    <t>User has product in the cart</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Times New Roman"/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve">1.. Leave required checkout fields blank and continue </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Times New Roman"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t>Place Order</t>
+    </r>
+  </si>
+  <si>
+    <t>Validation messages displayed</t>
+  </si>
+  <si>
+    <t>TC-015</t>
+  </si>
+  <si>
+    <t>Logout and use browser back button</t>
+  </si>
+  <si>
+    <t>User is logged in</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Times New Roman"/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve">1. Click </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Times New Roman"/>
+        <b/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve">Logout
+</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Times New Roman"/>
+        <color theme="1"/>
+        <sz val="12.0"/>
+      </rPr>
+      <t xml:space="preserve">2. Press browser back </t>
+    </r>
+  </si>
+  <si>
+    <t>User remains logout</t>
+  </si>
+  <si>
+    <t>Cached page accessible after logout</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-ZCsVyw1BYE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -593,6 +667,12 @@
     <font>
       <color theme="1"/>
       <name val="Comic Sans MS"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="3">
@@ -629,7 +709,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -647,6 +727,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -899,7 +982,9 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1"/>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -920,28 +1005,28 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
@@ -964,28 +1049,28 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
@@ -1008,30 +1093,32 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
-      <c r="I4" s="5"/>
+      <c r="I4" s="6" t="s">
+        <v>31</v>
+      </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -1052,28 +1139,28 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
@@ -1096,28 +1183,28 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
@@ -1140,30 +1227,32 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>39</v>
+      <c r="H7" s="4" t="s">
+        <v>30</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>40</v>
+      <c r="I7" s="6" t="s">
+        <v>48</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
@@ -1184,28 +1273,28 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
@@ -1228,30 +1317,32 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
-      <c r="I9" s="5"/>
+      <c r="I9" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
@@ -1272,28 +1363,28 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
@@ -1316,28 +1407,28 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
@@ -1360,28 +1451,28 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5"/>
@@ -1404,28 +1495,28 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
@@ -1448,28 +1539,28 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
@@ -1492,28 +1583,28 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
@@ -1536,30 +1627,32 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
-      <c r="I16" s="5"/>
+      <c r="I16" s="6" t="s">
+        <v>101</v>
+      </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
@@ -29391,6 +29484,12 @@
       <formula1>"Positive,Negative,Edge Case"</formula1>
     </dataValidation>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="I4"/>
+    <hyperlink r:id="rId2" ref="I7"/>
+    <hyperlink r:id="rId3" ref="I9"/>
+    <hyperlink r:id="rId4" ref="I16"/>
+  </hyperlinks>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>